--- a/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO-Agent运行结果-20260923-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO-Agent运行结果-20260923-V1.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="5" r:id="Rcbae858c342c4d9d"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent总览" sheetId="1" r:id="R5cdbbaa066e745d8"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="管理层摘要" sheetId="2" r:id="R2e063aab8727442c"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发现清单" sheetId="3" r:id="R5f89dff8cdd9494f"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据明细" sheetId="4" r:id="R2c52584916d24f4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="5" r:id="Rcbae858c342c4d9d"/>
   </x:sheets>
 </x:workbook>
 </file>
